--- a/input_processing/reg_estimates_ES_Cleaned/reg_RMSE.xlsx
+++ b/input_processing/reg_estimates_ES_Cleaned/reg_RMSE.xlsx
@@ -93,7 +93,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.0356942061615584</v>
+        <v>0.78482760577743338</v>
       </c>
     </row>
     <row r="3">
@@ -101,7 +101,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.0343433893627987</v>
+        <v>0.81220364204212658</v>
       </c>
     </row>
     <row r="4">
@@ -109,7 +109,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.39227908620241336</v>
+        <v>0.29965633365783223</v>
       </c>
     </row>
     <row r="5">
@@ -117,7 +117,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.36737261733128346</v>
+        <v>0.28215882296686756</v>
       </c>
     </row>
     <row r="6">
@@ -125,7 +125,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.72647449677507081</v>
+        <v>1.368326066957045</v>
       </c>
     </row>
   </sheetData>
